--- a/Simulation/Results/p.mid_Ten.Fixed.Ints_mean.surv.70.xlsx
+++ b/Simulation/Results/p.mid_Ten.Fixed.Ints_mean.surv.70.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">mid</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4 hours</t>
+    <t xml:space="preserve">5.5 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6 hours</t>
   </si>
 </sst>
 </file>
@@ -419,13 +419,13 @@
         <v>50</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0245</v>
+        <v>0.0232</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0077</v>
+        <v>0.0059</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0179</v>
+        <v>0.016</v>
       </c>
       <c r="E2" t="n">
         <v>0.0142857142857143</v>
@@ -448,13 +448,13 @@
         <v>100</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0221</v>
+        <v>0.0206</v>
       </c>
       <c r="C3" t="n">
-        <v>0.021</v>
+        <v>0.0186</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0326</v>
+        <v>0.0304</v>
       </c>
       <c r="E3" t="n">
         <v>0.0142857142857143</v>
@@ -477,13 +477,13 @@
         <v>200</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0336</v>
+        <v>0.0312</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0318</v>
+        <v>0.0322</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0662</v>
+        <v>0.0653</v>
       </c>
       <c r="E4" t="n">
         <v>0.0142857142857143</v>
@@ -506,13 +506,13 @@
         <v>500</v>
       </c>
       <c r="B5" t="n">
-        <v>0.041</v>
+        <v>0.0398</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0432</v>
+        <v>0.0428</v>
       </c>
       <c r="D5" t="n">
-        <v>0.071</v>
+        <v>0.07</v>
       </c>
       <c r="E5" t="n">
         <v>0.0142857142857143</v>
